--- a/test/integration/02-out.xlsx
+++ b/test/integration/02-out.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="244">
   <si>
     <t>variable</t>
   </si>
@@ -27,6 +27,9 @@
   </si>
   <si>
     <t>name</t>
+  </si>
+  <si>
+    <t>method</t>
   </si>
   <si>
     <t>Buğday, Durum Buğdayı Hariç</t>
@@ -356,9 +359,6 @@
     <t>Sermaye Temini</t>
   </si>
   <si>
-    <t>{}</t>
-  </si>
-  <si>
     <t>constraint</t>
   </si>
   <si>
@@ -368,10 +368,52 @@
     <t>rhs</t>
   </si>
   <si>
-    <t>Toplam Arazi</t>
+    <t>&lt;=</t>
   </si>
   <si>
-    <t>&lt;=</t>
+    <t>=</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>OPTIMAL</t>
+  </si>
+  <si>
+    <t>Solution is optimal</t>
+  </si>
+  <si>
+    <t>reduced_cost</t>
+  </si>
+  <si>
+    <t>original_value</t>
+  </si>
+  <si>
+    <t>lower_bound</t>
+  </si>
+  <si>
+    <t>upper_bound</t>
+  </si>
+  <si>
+    <t>is_basic_variable</t>
+  </si>
+  <si>
+    <t>shadow_price</t>
+  </si>
+  <si>
+    <t>slack_or_surplus</t>
+  </si>
+  <si>
+    <t>neither_bounds_are_binding</t>
+  </si>
+  <si>
+    <t>Toplam Arazi</t>
   </si>
   <si>
     <t>Toplam Kuru Tarla Arazisi</t>
@@ -381,9 +423,6 @@
   </si>
   <si>
     <t>Toplam Meyve Arazisi</t>
-  </si>
-  <si>
-    <t>=</t>
   </si>
   <si>
     <t>Toplam Sebze Arazisi</t>
@@ -711,45 +750,6 @@
   </si>
   <si>
     <t>Ağıl Yeri</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>OPTIMAL</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Solution is optimal</t>
-  </si>
-  <si>
-    <t>reduced_cost</t>
-  </si>
-  <si>
-    <t>original_value</t>
-  </si>
-  <si>
-    <t>lower_bound</t>
-  </si>
-  <si>
-    <t>upper_bound</t>
-  </si>
-  <si>
-    <t>is_basic_variable</t>
-  </si>
-  <si>
-    <t>shadow_price</t>
-  </si>
-  <si>
-    <t>slack_or_surplus</t>
-  </si>
-  <si>
-    <t>neither_bounds_are_binding</t>
   </si>
 </sst>
 </file>
@@ -1081,15 +1081,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1099,125 +1100,125 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>-116.27</v>
       </c>
-      <c r="C2" t="s">
-        <v>112</v>
-      </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2.2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>-445.33</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>2.2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>-218.37</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>2.48</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>-454.21</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>2.48</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>-126.32</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>-489.65</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>1.1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>-326.56</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>3.5</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>-2905.21</v>
@@ -1225,7 +1226,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -1233,7 +1234,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>-2745.98</v>
@@ -1241,7 +1242,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>1.7</v>
@@ -1249,7 +1250,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>-952.12</v>
@@ -1257,7 +1258,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>0.45</v>
@@ -1265,7 +1266,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>-485.16</v>
@@ -1273,7 +1274,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>1.15</v>
@@ -1281,7 +1282,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>-485.16</v>
@@ -1289,7 +1290,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>1.15</v>
@@ -1297,7 +1298,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>-624.41</v>
@@ -1305,7 +1306,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>1.65</v>
@@ -1313,7 +1314,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>-715.3200000000001</v>
@@ -1321,7 +1322,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>1.95</v>
@@ -1329,7 +1330,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>-677.6</v>
@@ -1337,7 +1338,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>0.42</v>
@@ -1345,7 +1346,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>-598.63</v>
@@ -1353,7 +1354,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>1.5</v>
@@ -1361,7 +1362,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>-546.23</v>
@@ -1369,7 +1370,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -1377,7 +1378,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>-412.65</v>
@@ -1385,7 +1386,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>5.25</v>
@@ -1393,7 +1394,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>-2689.74</v>
@@ -1401,7 +1402,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>1.05</v>
@@ -1409,7 +1410,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>-1369.41</v>
@@ -1417,7 +1418,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>2.75</v>
@@ -1425,7 +1426,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>-1369.41</v>
@@ -1433,7 +1434,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43">
         <v>2.5</v>
@@ -1441,7 +1442,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44">
         <v>-2189</v>
@@ -1449,7 +1450,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -1457,7 +1458,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>-592.36</v>
@@ -1465,7 +1466,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>2.6</v>
@@ -1473,7 +1474,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>-3245.63</v>
@@ -1481,7 +1482,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>1.86</v>
@@ -1489,7 +1490,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>-3015.65</v>
@@ -1497,7 +1498,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51">
         <v>2.25</v>
@@ -1505,7 +1506,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52">
         <v>-4282.23</v>
@@ -1513,7 +1514,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>2.25</v>
@@ -1521,7 +1522,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54">
         <v>-4136.45</v>
@@ -1529,7 +1530,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55">
         <v>1.63</v>
@@ -1537,7 +1538,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B56">
         <v>-5749.67</v>
@@ -1545,7 +1546,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B57">
         <v>1.63</v>
@@ -1553,7 +1554,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58">
         <v>-1345.68</v>
@@ -1561,7 +1562,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B59">
         <v>1.75</v>
@@ -1569,7 +1570,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60">
         <v>-1945.65</v>
@@ -1577,7 +1578,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B61">
         <v>2.5</v>
@@ -1585,7 +1586,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62">
         <v>-1881.84</v>
@@ -1593,7 +1594,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B63">
         <v>3.5</v>
@@ -1601,7 +1602,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64">
         <v>-2311.88</v>
@@ -1609,7 +1610,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65">
         <v>3.25</v>
@@ -1617,7 +1618,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66">
         <v>-2311.88</v>
@@ -1625,7 +1626,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B67">
         <v>5</v>
@@ -1633,7 +1634,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B68">
         <v>-1670.43</v>
@@ -1641,7 +1642,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B69">
         <v>10</v>
@@ -1649,7 +1650,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70">
         <v>-1089</v>
@@ -1657,7 +1658,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B71">
         <v>7</v>
@@ -1665,7 +1666,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B72">
         <v>-9195.27</v>
@@ -1673,7 +1674,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B73">
         <v>5.5</v>
@@ -1681,7 +1682,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B74">
         <v>-9841.860000000001</v>
@@ -1689,7 +1690,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75">
         <v>45</v>
@@ -1697,7 +1698,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76">
         <v>-1041.25</v>
@@ -1705,7 +1706,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77">
         <v>8</v>
@@ -1713,7 +1714,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B78">
         <v>-5000</v>
@@ -1721,7 +1722,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B79">
         <v>4.5</v>
@@ -1729,7 +1730,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B80">
         <v>-8814.299999999999</v>
@@ -1737,7 +1738,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B81">
         <v>4.5</v>
@@ -1745,7 +1746,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B82">
         <v>-156.45</v>
@@ -1753,7 +1754,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B83">
         <v>2.5</v>
@@ -1761,7 +1762,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B84">
         <v>-135.56</v>
@@ -1769,7 +1770,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -1777,7 +1778,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B86">
         <v>-482.66</v>
@@ -1785,7 +1786,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B87">
         <v>5.6</v>
@@ -1793,7 +1794,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B88">
         <v>-384.56</v>
@@ -1801,7 +1802,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B89">
         <v>4.5</v>
@@ -1809,7 +1810,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B90">
         <v>-426.56</v>
@@ -1817,7 +1818,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B91">
         <v>3.5</v>
@@ -1825,7 +1826,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B92">
         <v>-542.12</v>
@@ -1833,7 +1834,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B93">
         <v>5.6</v>
@@ -1841,7 +1842,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B94">
         <v>-1049.23</v>
@@ -1849,7 +1850,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B95">
         <v>15</v>
@@ -1857,7 +1858,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B96">
         <v>-336.15</v>
@@ -1865,7 +1866,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B97">
         <v>2.5</v>
@@ -1873,7 +1874,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B98">
         <v>-17.43</v>
@@ -1881,7 +1882,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B99">
         <v>-17.43</v>
@@ -1889,7 +1890,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B100">
         <v>-17.43</v>
@@ -1897,7 +1898,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B101">
         <v>-17.43</v>
@@ -1905,7 +1906,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B102">
         <v>-17.43</v>
@@ -1913,7 +1914,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B103">
         <v>-17.43</v>
@@ -1921,7 +1922,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B104">
         <v>-17.43</v>
@@ -1929,7 +1930,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B105">
         <v>-17.43</v>
@@ -1937,7 +1938,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B106">
         <v>-17.43</v>
@@ -1945,7 +1946,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B107">
         <v>-17.43</v>
@@ -1953,7 +1954,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B108">
         <v>-17.43</v>
@@ -1961,7 +1962,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B109">
         <v>-17.43</v>
@@ -1969,7 +1970,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B110">
         <v>-0.25</v>
@@ -1985,7 +1986,7 @@
   <dimension ref="A1:DH114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="3.5703125" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" customWidth="1"/>
@@ -2110,339 +2111,336 @@
         <v>115</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AK1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AL1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AM1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AN1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AO1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AP1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AQ1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AR1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AS1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AT1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AU1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AV1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AW1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AX1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AY1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AZ1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="BA1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BB1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BC1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BD1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BE1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BF1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BG1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BH1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BI1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BJ1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BK1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BL1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BM1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BN1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BO1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BP1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BQ1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BR1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BS1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BT1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BU1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="BV1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BW1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BX1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BY1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BZ1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CA1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CB1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CC1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CD1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CE1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="CF1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="CG1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="CH1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="CI1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="CJ1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="CK1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="CL1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="CM1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="CN1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="CO1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="CP1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="CQ1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="CR1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="CS1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="CT1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="CU1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="CV1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="CW1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="CX1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="CY1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="CZ1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="DA1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="DB1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="DC1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="DD1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="DE1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="DF1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="DG1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="DH1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:112">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>116</v>
-      </c>
-      <c r="B2" t="s">
-        <v>117</v>
       </c>
       <c r="C2">
         <v>1143058</v>
@@ -2776,11 +2774,8 @@
       </c>
     </row>
     <row r="3" spans="1:112">
-      <c r="A3" t="s">
-        <v>118</v>
-      </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3">
         <v>933464.6800000001</v>
@@ -3114,11 +3109,8 @@
       </c>
     </row>
     <row r="4" spans="1:112">
-      <c r="A4" t="s">
-        <v>119</v>
-      </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4">
         <v>110760.32</v>
@@ -3452,11 +3444,8 @@
       </c>
     </row>
     <row r="5" spans="1:112">
-      <c r="A5" t="s">
-        <v>120</v>
-      </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C5">
         <v>1700</v>
@@ -3790,11 +3779,8 @@
       </c>
     </row>
     <row r="6" spans="1:112">
-      <c r="A6" t="s">
-        <v>122</v>
-      </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6">
         <v>2693</v>
@@ -4128,11 +4114,8 @@
       </c>
     </row>
     <row r="7" spans="1:112">
-      <c r="A7" t="s">
-        <v>123</v>
-      </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C7">
         <v>34</v>
@@ -4466,11 +4449,8 @@
       </c>
     </row>
     <row r="8" spans="1:112">
-      <c r="A8" t="s">
-        <v>124</v>
-      </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -4804,11 +4784,8 @@
       </c>
     </row>
     <row r="9" spans="1:112">
-      <c r="A9" t="s">
-        <v>125</v>
-      </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9">
         <v>217095</v>
@@ -5142,11 +5119,8 @@
       </c>
     </row>
     <row r="10" spans="1:112">
-      <c r="A10" t="s">
-        <v>126</v>
-      </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C10">
         <v>62344.5</v>
@@ -5480,11 +5454,8 @@
       </c>
     </row>
     <row r="11" spans="1:112">
-      <c r="A11" t="s">
-        <v>127</v>
-      </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11">
         <v>157138.5</v>
@@ -5818,11 +5789,8 @@
       </c>
     </row>
     <row r="12" spans="1:112">
-      <c r="A12" t="s">
-        <v>128</v>
-      </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12">
         <v>89521.5</v>
@@ -6156,11 +6124,8 @@
       </c>
     </row>
     <row r="13" spans="1:112">
-      <c r="A13" t="s">
-        <v>129</v>
-      </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13">
         <v>1303.5</v>
@@ -6494,11 +6459,8 @@
       </c>
     </row>
     <row r="14" spans="1:112">
-      <c r="A14" t="s">
-        <v>130</v>
-      </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14">
         <v>197191.5</v>
@@ -6832,11 +6794,8 @@
       </c>
     </row>
     <row r="15" spans="1:112">
-      <c r="A15" t="s">
-        <v>131</v>
-      </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C15">
         <v>26476.5</v>
@@ -7170,11 +7129,8 @@
       </c>
     </row>
     <row r="16" spans="1:112">
-      <c r="A16" t="s">
-        <v>132</v>
-      </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16">
         <v>518.1</v>
@@ -7507,12 +7463,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:112">
-      <c r="A17" t="s">
-        <v>133</v>
-      </c>
+    <row r="17" spans="2:112">
       <c r="B17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C17">
         <v>8698.5</v>
@@ -7845,12 +7798,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:112">
-      <c r="A18" t="s">
-        <v>134</v>
-      </c>
+    <row r="18" spans="2:112">
       <c r="B18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18">
         <v>18943.5</v>
@@ -8183,12 +8133,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:112">
-      <c r="A19" t="s">
-        <v>135</v>
-      </c>
+    <row r="19" spans="2:112">
       <c r="B19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19">
         <v>52444.5</v>
@@ -8521,12 +8468,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:112">
-      <c r="A20" t="s">
-        <v>136</v>
-      </c>
+    <row r="20" spans="2:112">
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20">
         <v>345</v>
@@ -8859,12 +8803,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:112">
-      <c r="A21" t="s">
-        <v>137</v>
-      </c>
+    <row r="21" spans="2:112">
       <c r="B21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C21">
         <v>212472.7</v>
@@ -9197,12 +9138,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:112">
-      <c r="A22" t="s">
-        <v>138</v>
-      </c>
+    <row r="22" spans="2:112">
       <c r="B22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C22">
         <v>110056.1</v>
@@ -9535,12 +9473,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:112">
-      <c r="A23" t="s">
-        <v>139</v>
-      </c>
+    <row r="23" spans="2:112">
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23">
         <v>7635</v>
@@ -9873,12 +9808,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:112">
-      <c r="A24" t="s">
-        <v>140</v>
-      </c>
+    <row r="24" spans="2:112">
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24">
         <v>100568.6</v>
@@ -10211,12 +10143,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:112">
-      <c r="A25" t="s">
-        <v>141</v>
-      </c>
+    <row r="25" spans="2:112">
       <c r="B25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25">
         <v>3521.1</v>
@@ -10549,12 +10478,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:112">
-      <c r="A26" t="s">
-        <v>142</v>
-      </c>
+    <row r="26" spans="2:112">
       <c r="B26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C26">
         <v>119.9</v>
@@ -10887,12 +10813,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:112">
-      <c r="A27" t="s">
-        <v>143</v>
-      </c>
+    <row r="27" spans="2:112">
       <c r="B27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27">
         <v>1608.2</v>
@@ -11225,12 +11148,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:112">
-      <c r="A28" t="s">
-        <v>144</v>
-      </c>
+    <row r="28" spans="2:112">
       <c r="B28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C28">
         <v>18</v>
@@ -11563,12 +11483,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:112">
-      <c r="A29" t="s">
-        <v>145</v>
-      </c>
+    <row r="29" spans="2:112">
       <c r="B29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C29">
         <v>3.6</v>
@@ -11901,12 +11818,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:112">
-      <c r="A30" t="s">
-        <v>146</v>
-      </c>
+    <row r="30" spans="2:112">
       <c r="B30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C30">
         <v>8.4</v>
@@ -12239,12 +12153,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:112">
-      <c r="A31" t="s">
-        <v>147</v>
-      </c>
+    <row r="31" spans="2:112">
       <c r="B31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31">
         <v>5.5</v>
@@ -12577,12 +12488,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:112">
-      <c r="A32" t="s">
-        <v>148</v>
-      </c>
+    <row r="32" spans="2:112">
       <c r="B32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C32">
         <v>13.2</v>
@@ -12915,12 +12823,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:112">
-      <c r="A33" t="s">
-        <v>149</v>
-      </c>
+    <row r="33" spans="2:112">
       <c r="B33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33">
         <v>181.5</v>
@@ -13253,12 +13158,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:112">
-      <c r="A34" t="s">
-        <v>150</v>
-      </c>
+    <row r="34" spans="2:112">
       <c r="B34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C34">
         <v>28.6</v>
@@ -13591,12 +13493,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:112">
-      <c r="A35" t="s">
-        <v>151</v>
-      </c>
+    <row r="35" spans="2:112">
       <c r="B35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C35">
         <v>391.6</v>
@@ -13929,12 +13828,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:112">
-      <c r="A36" t="s">
-        <v>152</v>
-      </c>
+    <row r="36" spans="2:112">
       <c r="B36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C36">
         <v>8.800000000000001</v>
@@ -14267,12 +14163,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:112">
-      <c r="A37" t="s">
-        <v>153</v>
-      </c>
+    <row r="37" spans="2:112">
       <c r="B37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C37">
         <v>68.2</v>
@@ -14605,12 +14498,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:112">
-      <c r="A38" t="s">
-        <v>154</v>
-      </c>
+    <row r="38" spans="2:112">
       <c r="B38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C38">
         <v>8.800000000000001</v>
@@ -14943,12 +14833,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:112">
-      <c r="A39" t="s">
-        <v>155</v>
-      </c>
+    <row r="39" spans="2:112">
       <c r="B39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C39">
         <v>19.8</v>
@@ -15281,12 +15168,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:112">
-      <c r="A40" t="s">
-        <v>156</v>
-      </c>
+    <row r="40" spans="2:112">
       <c r="B40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C40">
         <v>800</v>
@@ -15619,12 +15503,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:112">
-      <c r="A41" t="s">
-        <v>157</v>
-      </c>
+    <row r="41" spans="2:112">
       <c r="B41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C41">
         <v>145</v>
@@ -15957,12 +15838,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:112">
-      <c r="A42" t="s">
-        <v>158</v>
-      </c>
+    <row r="42" spans="2:112">
       <c r="B42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C42">
         <v>310</v>
@@ -16295,12 +16173,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:112">
-      <c r="A43" t="s">
-        <v>159</v>
-      </c>
+    <row r="43" spans="2:112">
       <c r="B43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C43">
         <v>445</v>
@@ -16633,12 +16508,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:112">
-      <c r="A44" t="s">
-        <v>160</v>
-      </c>
+    <row r="44" spans="2:112">
       <c r="B44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C44">
         <v>53197.5</v>
@@ -16971,12 +16843,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:112">
-      <c r="A45" t="s">
-        <v>161</v>
-      </c>
+    <row r="45" spans="2:112">
       <c r="B45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C45">
         <v>1584</v>
@@ -17309,12 +17178,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:112">
-      <c r="A46" t="s">
-        <v>162</v>
-      </c>
+    <row r="46" spans="2:112">
       <c r="B46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C46">
         <v>4187.3</v>
@@ -17647,12 +17513,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:112">
-      <c r="A47" t="s">
-        <v>163</v>
-      </c>
+    <row r="47" spans="2:112">
       <c r="B47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C47">
         <v>3029</v>
@@ -17985,12 +17848,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:112">
-      <c r="A48" t="s">
-        <v>164</v>
-      </c>
+    <row r="48" spans="2:112">
       <c r="B48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C48">
         <v>2575.1</v>
@@ -18323,12 +18183,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:112">
-      <c r="A49" t="s">
-        <v>165</v>
-      </c>
+    <row r="49" spans="2:112">
       <c r="B49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C49">
         <v>907.5000000000001</v>
@@ -18661,12 +18518,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:112">
-      <c r="A50" t="s">
-        <v>166</v>
-      </c>
+    <row r="50" spans="2:112">
       <c r="B50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C50">
         <v>3734.9</v>
@@ -18999,12 +18853,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:112">
-      <c r="A51" t="s">
-        <v>167</v>
-      </c>
+    <row r="51" spans="2:112">
       <c r="B51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C51">
         <v>1575</v>
@@ -19337,12 +19188,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:112">
-      <c r="A52" t="s">
-        <v>168</v>
-      </c>
+    <row r="52" spans="2:112">
       <c r="B52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -19675,12 +19523,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:112">
-      <c r="A53" t="s">
-        <v>169</v>
-      </c>
+    <row r="53" spans="2:112">
       <c r="B53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -20013,12 +19858,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:112">
-      <c r="A54" t="s">
-        <v>170</v>
-      </c>
+    <row r="54" spans="2:112">
       <c r="B54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -20351,12 +20193,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:112">
-      <c r="A55" t="s">
-        <v>171</v>
-      </c>
+    <row r="55" spans="2:112">
       <c r="B55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -20689,12 +20528,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:112">
-      <c r="A56" t="s">
-        <v>172</v>
-      </c>
+    <row r="56" spans="2:112">
       <c r="B56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -21027,12 +20863,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:112">
-      <c r="A57" t="s">
-        <v>173</v>
-      </c>
+    <row r="57" spans="2:112">
       <c r="B57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -21365,12 +21198,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:112">
-      <c r="A58" t="s">
-        <v>174</v>
-      </c>
+    <row r="58" spans="2:112">
       <c r="B58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -21703,12 +21533,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:112">
-      <c r="A59" t="s">
-        <v>175</v>
-      </c>
+    <row r="59" spans="2:112">
       <c r="B59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -22041,12 +21868,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:112">
-      <c r="A60" t="s">
-        <v>176</v>
-      </c>
+    <row r="60" spans="2:112">
       <c r="B60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -22379,12 +22203,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:112">
-      <c r="A61" t="s">
-        <v>177</v>
-      </c>
+    <row r="61" spans="2:112">
       <c r="B61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -22717,12 +22538,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:112">
-      <c r="A62" t="s">
-        <v>178</v>
-      </c>
+    <row r="62" spans="2:112">
       <c r="B62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -23055,12 +22873,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:112">
-      <c r="A63" t="s">
-        <v>179</v>
-      </c>
+    <row r="63" spans="2:112">
       <c r="B63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -23393,12 +23208,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:112">
-      <c r="A64" t="s">
-        <v>180</v>
-      </c>
+    <row r="64" spans="2:112">
       <c r="B64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -23731,12 +23543,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:112">
-      <c r="A65" t="s">
-        <v>181</v>
-      </c>
+    <row r="65" spans="2:112">
       <c r="B65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -24069,12 +23878,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:112">
-      <c r="A66" t="s">
-        <v>182</v>
-      </c>
+    <row r="66" spans="2:112">
       <c r="B66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -24407,12 +24213,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:112">
-      <c r="A67" t="s">
-        <v>183</v>
-      </c>
+    <row r="67" spans="2:112">
       <c r="B67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -24745,12 +24548,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:112">
-      <c r="A68" t="s">
-        <v>184</v>
-      </c>
+    <row r="68" spans="2:112">
       <c r="B68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -25083,12 +24883,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:112">
-      <c r="A69" t="s">
-        <v>185</v>
-      </c>
+    <row r="69" spans="2:112">
       <c r="B69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -25421,12 +25218,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:112">
-      <c r="A70" t="s">
-        <v>186</v>
-      </c>
+    <row r="70" spans="2:112">
       <c r="B70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -25759,12 +25553,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:112">
-      <c r="A71" t="s">
-        <v>187</v>
-      </c>
+    <row r="71" spans="2:112">
       <c r="B71" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -26097,12 +25888,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:112">
-      <c r="A72" t="s">
-        <v>188</v>
-      </c>
+    <row r="72" spans="2:112">
       <c r="B72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -26435,12 +26223,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:112">
-      <c r="A73" t="s">
-        <v>189</v>
-      </c>
+    <row r="73" spans="2:112">
       <c r="B73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -26773,12 +26558,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:112">
-      <c r="A74" t="s">
-        <v>190</v>
-      </c>
+    <row r="74" spans="2:112">
       <c r="B74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -27111,12 +26893,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:112">
-      <c r="A75" t="s">
-        <v>191</v>
-      </c>
+    <row r="75" spans="2:112">
       <c r="B75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -27449,12 +27228,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:112">
-      <c r="A76" t="s">
-        <v>192</v>
-      </c>
+    <row r="76" spans="2:112">
       <c r="B76" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -27787,12 +27563,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:112">
-      <c r="A77" t="s">
-        <v>193</v>
-      </c>
+    <row r="77" spans="2:112">
       <c r="B77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -28125,12 +27898,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:112">
-      <c r="A78" t="s">
-        <v>194</v>
-      </c>
+    <row r="78" spans="2:112">
       <c r="B78" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -28463,12 +28233,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:112">
-      <c r="A79" t="s">
-        <v>195</v>
-      </c>
+    <row r="79" spans="2:112">
       <c r="B79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -28801,12 +28568,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:112">
-      <c r="A80" t="s">
-        <v>196</v>
-      </c>
+    <row r="80" spans="2:112">
       <c r="B80" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -29139,12 +28903,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:112">
-      <c r="A81" t="s">
-        <v>197</v>
-      </c>
+    <row r="81" spans="2:112">
       <c r="B81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -29477,12 +29238,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:112">
-      <c r="A82" t="s">
-        <v>198</v>
-      </c>
+    <row r="82" spans="2:112">
       <c r="B82" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -29815,12 +29573,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:112">
-      <c r="A83" t="s">
-        <v>199</v>
-      </c>
+    <row r="83" spans="2:112">
       <c r="B83" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -30153,12 +29908,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:112">
-      <c r="A84" t="s">
-        <v>200</v>
-      </c>
+    <row r="84" spans="2:112">
       <c r="B84" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -30491,12 +30243,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:112">
-      <c r="A85" t="s">
-        <v>201</v>
-      </c>
+    <row r="85" spans="2:112">
       <c r="B85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -30829,12 +30578,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:112">
-      <c r="A86" t="s">
-        <v>202</v>
-      </c>
+    <row r="86" spans="2:112">
       <c r="B86" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -31167,12 +30913,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:112">
-      <c r="A87" t="s">
-        <v>203</v>
-      </c>
+    <row r="87" spans="2:112">
       <c r="B87" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -31505,12 +31248,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:112">
-      <c r="A88" t="s">
-        <v>204</v>
-      </c>
+    <row r="88" spans="2:112">
       <c r="B88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -31843,12 +31583,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:112">
-      <c r="A89" t="s">
-        <v>205</v>
-      </c>
+    <row r="89" spans="2:112">
       <c r="B89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -32181,12 +31918,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:112">
-      <c r="A90" t="s">
-        <v>206</v>
-      </c>
+    <row r="90" spans="2:112">
       <c r="B90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -32519,12 +32253,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:112">
-      <c r="A91" t="s">
-        <v>207</v>
-      </c>
+    <row r="91" spans="2:112">
       <c r="B91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -32857,12 +32588,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:112">
-      <c r="A92" t="s">
-        <v>208</v>
-      </c>
+    <row r="92" spans="2:112">
       <c r="B92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -33195,12 +32923,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:112">
-      <c r="A93" t="s">
-        <v>209</v>
-      </c>
+    <row r="93" spans="2:112">
       <c r="B93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -33533,12 +33258,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:112">
-      <c r="A94" t="s">
-        <v>210</v>
-      </c>
+    <row r="94" spans="2:112">
       <c r="B94" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -33871,12 +33593,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:112">
-      <c r="A95" t="s">
-        <v>211</v>
-      </c>
+    <row r="95" spans="2:112">
       <c r="B95" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -34209,12 +33928,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:112">
-      <c r="A96" t="s">
-        <v>212</v>
-      </c>
+    <row r="96" spans="2:112">
       <c r="B96" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -34547,12 +34263,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:112">
-      <c r="A97" t="s">
-        <v>213</v>
-      </c>
+    <row r="97" spans="2:112">
       <c r="B97" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -34885,12 +34598,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:112">
-      <c r="A98" t="s">
-        <v>214</v>
-      </c>
+    <row r="98" spans="2:112">
       <c r="B98" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -35223,12 +34933,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:112">
-      <c r="A99" t="s">
-        <v>215</v>
-      </c>
+    <row r="99" spans="2:112">
       <c r="B99" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -35561,12 +35268,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:112">
-      <c r="A100" t="s">
-        <v>216</v>
-      </c>
+    <row r="100" spans="2:112">
       <c r="B100" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C100">
         <v>10486180</v>
@@ -35899,12 +35603,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:112">
-      <c r="A101" t="s">
-        <v>217</v>
-      </c>
+    <row r="101" spans="2:112">
       <c r="B101" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C101">
         <v>13588972</v>
@@ -36237,12 +35938,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:112">
-      <c r="A102" t="s">
-        <v>218</v>
-      </c>
+    <row r="102" spans="2:112">
       <c r="B102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C102">
         <v>14234509</v>
@@ -36575,12 +36273,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:112">
-      <c r="A103" t="s">
-        <v>219</v>
-      </c>
+    <row r="103" spans="2:112">
       <c r="B103" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C103">
         <v>14095596</v>
@@ -36913,12 +36608,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:112">
-      <c r="A104" t="s">
-        <v>220</v>
-      </c>
+    <row r="104" spans="2:112">
       <c r="B104" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C104">
         <v>14234509</v>
@@ -37251,12 +36943,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:112">
-      <c r="A105" t="s">
-        <v>221</v>
-      </c>
+    <row r="105" spans="2:112">
       <c r="B105" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C105">
         <v>14095596</v>
@@ -37589,12 +37278,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:112">
-      <c r="A106" t="s">
-        <v>222</v>
-      </c>
+    <row r="106" spans="2:112">
       <c r="B106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C106">
         <v>14234509</v>
@@ -37927,12 +37613,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:112">
-      <c r="A107" t="s">
-        <v>223</v>
-      </c>
+    <row r="107" spans="2:112">
       <c r="B107" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C107">
         <v>14234509</v>
@@ -38265,12 +37948,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:112">
-      <c r="A108" t="s">
-        <v>224</v>
-      </c>
+    <row r="108" spans="2:112">
       <c r="B108" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C108">
         <v>14095596</v>
@@ -38603,12 +38283,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:112">
-      <c r="A109" t="s">
-        <v>225</v>
-      </c>
+    <row r="109" spans="2:112">
       <c r="B109" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C109">
         <v>14234509</v>
@@ -38941,12 +38618,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:112">
-      <c r="A110" t="s">
-        <v>226</v>
-      </c>
+    <row r="110" spans="2:112">
       <c r="B110" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C110">
         <v>14095596</v>
@@ -39279,12 +38953,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:112">
-      <c r="A111" t="s">
-        <v>227</v>
-      </c>
+    <row r="111" spans="2:112">
       <c r="B111" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C111">
         <v>14234509</v>
@@ -39617,12 +39288,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:112">
-      <c r="A112" t="s">
-        <v>228</v>
-      </c>
+    <row r="112" spans="2:112">
       <c r="B112" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C112">
         <v>2189124194.78</v>
@@ -39955,12 +39623,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="113" spans="1:112">
-      <c r="A113" t="s">
-        <v>229</v>
-      </c>
+    <row r="113" spans="2:112">
       <c r="B113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C113">
         <v>1260800</v>
@@ -40293,12 +39958,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:112">
-      <c r="A114" t="s">
-        <v>230</v>
-      </c>
+    <row r="114" spans="2:112">
       <c r="B114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C114">
         <v>1075200</v>
@@ -40638,35 +40300,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B1">
+        <v>118</v>
+      </c>
+      <c r="B1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2">
         <v>1506809780.475</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B3" t="s">
-        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -40693,27 +40354,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>120</v>
       </c>
       <c r="C1" t="s">
-        <v>236</v>
+        <v>123</v>
       </c>
       <c r="D1" t="s">
-        <v>237</v>
+        <v>124</v>
       </c>
       <c r="E1" t="s">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c r="F1" t="s">
-        <v>239</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>240</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>217095</v>
@@ -40736,7 +40397,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>43419000</v>
@@ -40759,7 +40420,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -40782,7 +40443,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -40805,7 +40466,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>129955.68</v>
@@ -40828,7 +40489,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>18583662.24</v>
@@ -40851,7 +40512,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -40874,7 +40535,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -40897,7 +40558,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -40920,7 +40581,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -40943,7 +40604,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>197191.5</v>
@@ -40966,7 +40627,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>269757972</v>
@@ -40989,7 +40650,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>26476.5</v>
@@ -41012,7 +40673,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>8260668</v>
@@ -41035,7 +40696,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>518.1</v>
@@ -41058,7 +40719,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>545559.3</v>
@@ -41081,7 +40742,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>8698.5</v>
@@ -41104,7 +40765,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>24503674.5</v>
@@ -41127,7 +40788,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>18943.5</v>
@@ -41150,7 +40811,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>52568212.5</v>
@@ -41173,7 +40834,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>52444.5</v>
@@ -41196,7 +40857,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>65765403</v>
@@ -41219,7 +40880,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>345</v>
@@ -41242,7 +40903,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>431940</v>
@@ -41265,7 +40926,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>110760.32</v>
@@ -41288,7 +40949,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>152184679.68</v>
@@ -41311,7 +40972,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>110056.1</v>
@@ -41334,7 +40995,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>134818722.5</v>
@@ -41357,7 +41018,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>7635</v>
@@ -41380,7 +41041,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>40915965</v>
@@ -41403,7 +41064,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>100568.6</v>
@@ -41426,7 +41087,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>120380614.2</v>
@@ -41449,7 +41110,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>3521.1</v>
@@ -41472,7 +41133,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>4929540</v>
@@ -41495,7 +41156,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>119.9</v>
@@ -41518,7 +41179,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>17625.3</v>
@@ -41541,7 +41202,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>1608.2</v>
@@ -41564,7 +41225,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>9970840</v>
@@ -41587,7 +41248,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>18</v>
@@ -41610,7 +41271,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>30060</v>
@@ -41633,7 +41294,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>3.6</v>
@@ -41656,7 +41317,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43">
         <v>6001.2</v>
@@ -41679,7 +41340,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -41702,7 +41363,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -41725,7 +41386,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -41748,7 +41409,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -41771,7 +41432,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -41794,7 +41455,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -41817,7 +41478,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>181.5</v>
@@ -41840,7 +41501,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51">
         <v>573177</v>
@@ -41863,7 +41524,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52">
         <v>28.6</v>
@@ -41886,7 +41547,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>114400</v>
@@ -41909,7 +41570,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54">
         <v>286.6</v>
@@ -41932,7 +41593,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55">
         <v>1096531.6</v>
@@ -41955,7 +41616,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B56">
         <v>5.4</v>
@@ -41978,7 +41639,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B57">
         <v>27000</v>
@@ -42001,7 +41662,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58">
         <v>68.2</v>
@@ -42024,7 +41685,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B59">
         <v>204600</v>
@@ -42047,7 +41708,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60">
         <v>8.800000000000001</v>
@@ -42070,7 +41731,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B61">
         <v>24200</v>
@@ -42093,7 +41754,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -42116,7 +41777,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -42139,7 +41800,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64">
         <v>800</v>
@@ -42162,7 +41823,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65">
         <v>627200</v>
@@ -42185,7 +41846,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66">
         <v>145</v>
@@ -42208,7 +41869,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B67">
         <v>158050</v>
@@ -42231,7 +41892,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B68">
         <v>310</v>
@@ -42254,7 +41915,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B69">
         <v>56110</v>
@@ -42277,7 +41938,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70">
         <v>445</v>
@@ -42300,7 +41961,7 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B71">
         <v>97010</v>
@@ -42323,7 +41984,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B72">
         <v>74324.734</v>
@@ -42346,7 +42007,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B73">
         <v>180609104.713</v>
@@ -42369,7 +42030,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B74">
         <v>105828.278</v>
@@ -42392,7 +42053,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75">
         <v>29631917.967</v>
@@ -42415,7 +42076,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -42438,7 +42099,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -42461,7 +42122,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -42484,7 +42145,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -42507,7 +42168,7 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -42530,7 +42191,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -42553,7 +42214,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B82">
         <v>53197.5</v>
@@ -42576,7 +42237,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B83">
         <v>6543292.5</v>
@@ -42599,7 +42260,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -42622,7 +42283,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -42645,7 +42306,7 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B86">
         <v>4187.3</v>
@@ -42668,7 +42329,7 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B87">
         <v>515037.9</v>
@@ -42691,7 +42352,7 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B88">
         <v>3029</v>
@@ -42714,7 +42375,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B89">
         <v>726960</v>
@@ -42737,7 +42398,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -42760,7 +42421,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -42783,7 +42444,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -42806,7 +42467,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -42829,7 +42490,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -42852,7 +42513,7 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -42875,7 +42536,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -42898,7 +42559,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -42921,7 +42582,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -42944,7 +42605,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -42967,7 +42628,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -42990,7 +42651,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -43013,7 +42674,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -43036,7 +42697,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -43059,7 +42720,7 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -43082,7 +42743,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -43105,7 +42766,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -43128,7 +42789,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -43151,7 +42812,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -43174,7 +42835,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -43197,7 +42858,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -43242,27 +42903,27 @@
         <v>113</v>
       </c>
       <c r="B1" t="s">
-        <v>241</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
-        <v>242</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
-        <v>237</v>
+        <v>124</v>
       </c>
       <c r="E1" t="s">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c r="F1" t="s">
-        <v>239</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>243</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -43285,7 +42946,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B3">
         <v>92.13800000000001</v>
@@ -43308,7 +42969,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B4">
         <v>1516.498</v>
@@ -43331,7 +42992,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B5">
         <v>-231.105</v>
@@ -43354,7 +43015,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B6">
         <v>1263.963</v>
@@ -43377,7 +43038,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B7">
         <v>1238.336</v>
@@ -43400,7 +43061,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -43423,7 +43084,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B9">
         <v>208.094</v>
@@ -43446,7 +43107,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -43469,7 +43130,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -43492,7 +43153,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -43515,7 +43176,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -43538,7 +43199,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B14">
         <v>824.0549999999999</v>
@@ -43561,7 +43222,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B15">
         <v>607.3049999999999</v>
@@ -43584,7 +43245,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B16">
         <v>508.691</v>
@@ -43607,7 +43268,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B17">
         <v>1395.826</v>
@@ -43630,7 +43291,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B18">
         <v>12.071</v>
@@ -43653,7 +43314,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B19">
         <v>766.752</v>
@@ -43676,7 +43337,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B20">
         <v>764.452</v>
@@ -43699,7 +43360,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -43722,7 +43383,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B22">
         <v>1436.728</v>
@@ -43745,7 +43406,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B23">
         <v>1344.101</v>
@@ -43768,7 +43429,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B24">
         <v>983.75</v>
@@ -43791,7 +43452,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B25">
         <v>651.24</v>
@@ -43814,7 +43475,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B26">
         <v>183.566</v>
@@ -43837,7 +43498,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B27">
         <v>2012.707</v>
@@ -43860,7 +43521,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B28">
         <v>1682.372</v>
@@ -43883,7 +43544,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B29">
         <v>1257.372</v>
@@ -43906,7 +43567,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -43929,7 +43590,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -43952,7 +43613,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -43975,7 +43636,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B33">
         <v>2216.431</v>
@@ -43998,7 +43659,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B34">
         <v>2614.006</v>
@@ -44021,7 +43682,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -44044,7 +43705,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -44067,7 +43728,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B37">
         <v>2368.398</v>
@@ -44090,7 +43751,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B38">
         <v>3272.175</v>
@@ -44113,7 +43774,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -44136,7 +43797,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -44159,7 +43820,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B41">
         <v>2902</v>
@@ -44182,7 +43843,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B42">
         <v>33.085</v>
@@ -44205,7 +43866,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B43">
         <v>448.021</v>
@@ -44228,7 +43889,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B44">
         <v>27.294</v>
@@ -44251,7 +43912,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -44274,7 +43935,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B46">
         <v>16.458</v>
@@ -44297,7 +43958,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B47">
         <v>525.583</v>
@@ -44320,7 +43981,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -44343,7 +44004,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -44366,7 +44027,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -44389,7 +44050,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -44412,7 +44073,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B52">
         <v>2.2</v>
@@ -44435,7 +44096,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B53">
         <v>2.2</v>
@@ -44458,7 +44119,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B54">
         <v>2.48</v>
@@ -44481,7 +44142,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B55">
         <v>2.48</v>
@@ -44504,7 +44165,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B56">
         <v>2.5</v>
@@ -44527,7 +44188,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B57">
         <v>1.1</v>
@@ -44550,7 +44211,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B58">
         <v>3.5</v>
@@ -44573,7 +44234,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B59">
         <v>5</v>
@@ -44596,7 +44257,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B60">
         <v>1.7</v>
@@ -44619,7 +44280,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B61">
         <v>0.45</v>
@@ -44642,7 +44303,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B62">
         <v>1.15</v>
@@ -44665,7 +44326,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B63">
         <v>1.15</v>
@@ -44688,7 +44349,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B64">
         <v>1.65</v>
@@ -44711,7 +44372,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B65">
         <v>1.95</v>
@@ -44734,7 +44395,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B66">
         <v>0.42</v>
@@ -44757,7 +44418,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B67">
         <v>1.5</v>
@@ -44780,7 +44441,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -44803,7 +44464,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B69">
         <v>5.25</v>
@@ -44826,7 +44487,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B70">
         <v>1.05</v>
@@ -44849,7 +44510,7 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B71">
         <v>2.75</v>
@@ -44872,7 +44533,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B72">
         <v>2.5</v>
@@ -44895,7 +44556,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B73">
         <v>4.545</v>
@@ -44918,7 +44579,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B74">
         <v>4.94</v>
@@ -44941,7 +44602,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B75">
         <v>1.86</v>
@@ -44964,7 +44625,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B76">
         <v>2.25</v>
@@ -44987,7 +44648,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B77">
         <v>2.25</v>
@@ -45010,7 +44671,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B78">
         <v>1.63</v>
@@ -45033,7 +44694,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B79">
         <v>1.63</v>
@@ -45056,7 +44717,7 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B80">
         <v>1.75</v>
@@ -45079,7 +44740,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B81">
         <v>2.5</v>
@@ -45102,7 +44763,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B82">
         <v>3.526</v>
@@ -45125,7 +44786,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B83">
         <v>3.25</v>
@@ -45148,7 +44809,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B84">
         <v>5</v>
@@ -45171,7 +44832,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B85">
         <v>10</v>
@@ -45194,7 +44855,7 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B86">
         <v>7</v>
@@ -45217,7 +44878,7 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B87">
         <v>5.5</v>
@@ -45240,7 +44901,7 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B88">
         <v>45</v>
@@ -45263,7 +44924,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B89">
         <v>8</v>
@@ -45286,7 +44947,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B90">
         <v>4.5</v>
@@ -45309,7 +44970,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B91">
         <v>4.5</v>
@@ -45332,7 +44993,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B92">
         <v>2.5</v>
@@ -45355,7 +45016,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -45378,7 +45039,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B94">
         <v>5.6</v>
@@ -45401,7 +45062,7 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B95">
         <v>4.5</v>
@@ -45424,7 +45085,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B96">
         <v>4.318</v>
@@ -45447,7 +45108,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B97">
         <v>11.006</v>
@@ -45470,7 +45131,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B98">
         <v>23.148</v>
@@ -45493,7 +45154,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B99">
         <v>2.5</v>
@@ -45516,7 +45177,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -45539,7 +45200,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -45562,7 +45223,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -45585,7 +45246,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -45608,7 +45269,7 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -45631,7 +45292,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -45654,7 +45315,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -45677,7 +45338,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -45700,7 +45361,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -45723,7 +45384,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -45746,7 +45407,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -45769,7 +45430,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -45792,7 +45453,7 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B112">
         <v>0.202</v>
@@ -45815,7 +45476,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B113">
         <v>200.816</v>
@@ -45838,7 +45499,7 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B114">
         <v>0</v>
